--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487515_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487515_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7338</v>
+        <v>1.8351</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9066</v>
+        <v>2.8208</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1728</v>
+        <v>-0.9857</v>
       </c>
       <c r="G2" t="n">
         <v>-0.1357</v>
@@ -610,13 +610,13 @@
         <v>0.9792</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3264</v>
+        <v>-0.2251</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1653</v>
+        <v>0.0794</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4916</v>
+        <v>-0.3045</v>
       </c>
       <c r="V2" t="n">
         <v>1.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3318</v>
+        <v>1.1018</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5212</v>
+        <v>2.4782</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1894</v>
+        <v>-1.3765</v>
       </c>
       <c r="G3" t="n">
         <v>0.7437</v>
@@ -688,13 +688,13 @@
         <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1964</v>
+        <v>-0.0337</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1317</v>
+        <v>-0.1747</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3281</v>
+        <v>0.141</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9109</v>
+        <v>1.0916</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2811</v>
+        <v>0.8093</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6298</v>
+        <v>0.2823</v>
       </c>
       <c r="G4" t="n">
         <v>0.3599</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2958</v>
+        <v>-0.1151</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7369</v>
+        <v>-0.2088</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4412</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>1.4344</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0764</v>
+        <v>0.1772</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3359</v>
+        <v>0.643</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4123</v>
+        <v>-0.4658</v>
       </c>
       <c r="G5" t="n">
         <v>-0.6347</v>
@@ -844,13 +844,13 @@
         <v>0.5875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0292</v>
+        <v>0.2244</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2376</v>
+        <v>0.0694</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2084</v>
+        <v>0.155</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4956</v>
+        <v>-0.6898</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2878</v>
+        <v>0.0402</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7834</v>
+        <v>-0.73</v>
       </c>
       <c r="G6" t="n">
         <v>0.6293</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4626</v>
+        <v>0.2685</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6405</v>
+        <v>0.3929</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1779</v>
+        <v>-0.1244</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6083</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q. HUANG</t>
+          <t>Y. REY CONDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5529</v>
+        <v>-1.4858</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1394</v>
+        <v>-1.2591</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4135</v>
+        <v>-0.2267</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1047</v>
+        <v>-1.4918</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1848</v>
+        <v>-0.2794</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0801</v>
+        <v>-1.2125</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4307</v>
+        <v>-1.3032</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2691</v>
+        <v>-0.621</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1617</v>
+        <v>-0.6822</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.326</v>
+        <v>-0.1886</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0843</v>
+        <v>0.3416</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2417</v>
+        <v>-0.5302</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3502</v>
+        <v>0.1958</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3585</v>
+        <v>-0.1898</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7962</v>
+        <v>0.0441</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4376</v>
+        <v>-0.2339</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. REY CONDE</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7231</v>
+        <v>-2.06</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5232</v>
+        <v>-1.8863</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1999</v>
+        <v>-0.1737</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4918</v>
+        <v>-2.1592</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2794</v>
+        <v>-2.5485</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2125</v>
+        <v>0.3893</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3032</v>
+        <v>-1.6332</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.621</v>
+        <v>-2.2798</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6822</v>
+        <v>0.6466</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1886</v>
+        <v>-0.5261</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3416</v>
+        <v>-0.2687</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5302</v>
+        <v>-0.2573</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1958</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4272</v>
+        <v>-0.3708</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.22</v>
+        <v>-0.4905</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2072</v>
+        <v>0.1197</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>M. RODRÍGUEZ BLANCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2706</v>
+        <v>-2.6249</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1504</v>
+        <v>-1.9775</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1202</v>
+        <v>-0.6474</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1592</v>
+        <v>-0.4356</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5485</v>
+        <v>-0.476</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3893</v>
+        <v>0.0404</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6332</v>
+        <v>0.0404</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.2798</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6466</v>
+        <v>0.0404</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5261</v>
+        <v>-0.476</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2687</v>
+        <v>-0.476</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2573</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1958</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5814</v>
+        <v>-0.1513</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7546</v>
+        <v>-0.0594</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1732</v>
+        <v>-0.0919</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6659</v>
+        <v>-0.2754</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5507</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ BLANCO</t>
+          <t>D. MASEDA SOILAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6516</v>
+        <v>-2.8609</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9775</v>
+        <v>-1.5667</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6741</v>
+        <v>-1.2942</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4356</v>
+        <v>-0.5334</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.476</v>
+        <v>0.2341</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0404</v>
+        <v>-0.7675</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0404</v>
+        <v>1.4801</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2.0007</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0404</v>
+        <v>-0.5206</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.476</v>
+        <v>-2.0135</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.476</v>
+        <v>-1.7665</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.2469</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7626</v>
+        <v>-3.3294</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.178</v>
+        <v>-0.2147</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0594</v>
+        <v>-0.3464</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1186</v>
+        <v>0.1317</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. MASEDA SOILAN</t>
+          <t>Q. HUANG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2273</v>
+        <v>-3.0077</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9331</v>
+        <v>-1.6744</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2942</v>
+        <v>-1.3333</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5334</v>
+        <v>0.1047</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2341</v>
+        <v>0.1848</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7675</v>
+        <v>-0.0801</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4801</v>
+        <v>1.4307</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0007</v>
+        <v>1.2691</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5206</v>
+        <v>0.1617</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0135</v>
+        <v>-1.326</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7665</v>
+        <v>-1.0843</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2469</v>
+        <v>-0.2417</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.3294</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.917</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.0963</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7128</v>
+        <v>0.2611</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1317</v>
+        <v>-0.3574</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2166</v>
+        <v>-0.6659</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2166</v>
+        <v>0.5507</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.2684</v>
+        <v>-7.1719</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8047</v>
+        <v>-6.029</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4637</v>
+        <v>-1.1429</v>
       </c>
       <c r="G12" t="n">
         <v>-6.1761</v>
@@ -1390,13 +1390,13 @@
         <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8217</v>
+        <v>-0.7252</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0339</v>
+        <v>-0.2582</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7877</v>
+        <v>-0.467</v>
       </c>
       <c r="V12" t="n">
         <v>1.492</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.2894</v>
+        <v>-15.6953</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.1957</v>
+        <v>-7.601500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.0937</v>
+        <v>-8.093900000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-9.728899999999999</v>
@@ -1456,10 +1456,10 @@
         <v>-5.411099999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.1981</v>
+        <v>-5.198099999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-8.813099999999999</v>
+        <v>-8.8131</v>
       </c>
       <c r="Q13" t="n">
         <v>-17.6263</v>
@@ -1468,16 +1468,16 @@
         <v>8.812900000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2233</v>
+        <v>-1.6291</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2849</v>
+        <v>-0.6910999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>-0.9379999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>4.4759</v>
+        <v>4.475899999999999</v>
       </c>
       <c r="W13" t="n">
         <v>9.8355</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.0804</v>
+        <v>10.7229</v>
       </c>
       <c r="E14" t="n">
-        <v>7.3808</v>
+        <v>7.4831</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6996</v>
+        <v>3.2398</v>
       </c>
       <c r="G14" t="n">
         <v>4.3202</v>
@@ -1546,13 +1546,13 @@
         <v>2.9377</v>
       </c>
       <c r="S14" t="n">
-        <v>0.13</v>
+        <v>0.7725</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3899</v>
+        <v>0.4923</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.26</v>
+        <v>0.2803</v>
       </c>
       <c r="V14" t="n">
         <v>3.8676</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BELLON LOPEZ</t>
+          <t>D. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9968</v>
+        <v>1.9643</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2486</v>
+        <v>1.0107</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7482</v>
+        <v>0.9536</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6914</v>
+        <v>0.7655</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5093</v>
+        <v>0.4975</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1821</v>
+        <v>0.2681</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6852</v>
+        <v>1.1624</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6447000000000001</v>
+        <v>1.0412</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0404</v>
+        <v>0.1212</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0062</v>
+        <v>-0.3969</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1354</v>
+        <v>-0.5437</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1416</v>
+        <v>0.1468</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3262</v>
+        <v>-0.1722</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5634</v>
+        <v>-0.1517</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2373</v>
+        <v>-0.0204</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. PAZ VAZQUEZ</t>
+          <t>A. BELLON LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7864</v>
+        <v>1.6409</v>
       </c>
       <c r="E16" t="n">
-        <v>0.806</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9804</v>
+        <v>0.8017</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7655</v>
+        <v>0.6914</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4975</v>
+        <v>0.5093</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2681</v>
+        <v>0.1821</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1624</v>
+        <v>0.6852</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0412</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1212</v>
+        <v>0.0404</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3969</v>
+        <v>0.0062</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5437</v>
+        <v>-0.1354</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1468</v>
+        <v>0.1416</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3501</v>
+        <v>-0.0297</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3564</v>
+        <v>0.1541</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0063</v>
+        <v>-0.1838</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MUJICA LANDAETA</t>
+          <t>J. FERNANDEZ PILLADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2871</v>
+        <v>0.9363</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2286</v>
+        <v>0.1165</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9415</v>
+        <v>0.8198</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2346</v>
+        <v>1.5532</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5645</v>
+        <v>2.9225</v>
       </c>
       <c r="I17" t="n">
-        <v>1.799</v>
+        <v>-1.3693</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4919</v>
+        <v>1.6761</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4781</v>
+        <v>2.9194</v>
       </c>
       <c r="L17" t="n">
-        <v>0.97</v>
+        <v>-1.2432</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2573</v>
+        <v>-0.1229</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0864</v>
+        <v>0.0031</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8290999999999999</v>
+        <v>-0.1261</v>
       </c>
       <c r="P17" t="n">
-        <v>2.546</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R17" t="n">
-        <v>2.546</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2151</v>
+        <v>0.6377</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7368</v>
+        <v>0.3194</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5217000000000001</v>
+        <v>0.3183</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.7086</v>
+        <v>-0.2754</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.7086</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ PILLADO</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2654</v>
+        <v>0.9359</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5258</v>
+        <v>-2.1097</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7396</v>
+        <v>3.0456</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5532</v>
+        <v>-0.4262</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9225</v>
+        <v>2.065</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3693</v>
+        <v>-2.4913</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6761</v>
+        <v>-0.6512</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9194</v>
+        <v>1.9921</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2432</v>
+        <v>-2.6433</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1229</v>
+        <v>0.2249</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0031</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1261</v>
+        <v>0.152</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1543</v>
+        <v>-1.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9668</v>
+        <v>0.5787</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7287</v>
+        <v>-0.2835</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2381</v>
+        <v>0.8622</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>L. GARCÍA SINDIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1294</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3144</v>
+        <v>1.158</v>
       </c>
       <c r="F19" t="n">
-        <v>3.4438</v>
+        <v>-0.2361</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4262</v>
+        <v>1.8091</v>
       </c>
       <c r="H19" t="n">
-        <v>2.065</v>
+        <v>-0.9176</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4913</v>
+        <v>2.7267</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6512</v>
+        <v>2.2778</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9921</v>
+        <v>0.1021</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.6433</v>
+        <v>2.1757</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2249</v>
+        <v>-0.4687</v>
       </c>
       <c r="N19" t="n">
-        <v>0.07290000000000001</v>
+        <v>-1.0197</v>
       </c>
       <c r="O19" t="n">
-        <v>0.152</v>
+        <v>0.551</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1751</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9585</v>
+        <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7722</v>
+        <v>0.213</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4882</v>
+        <v>-0.1406</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2604</v>
+        <v>0.3536</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.675</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="E20" t="n">
         <v>-0.8641</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5391</v>
+        <v>1.7023</v>
       </c>
       <c r="G20" t="n">
         <v>0.4833</v>
@@ -2014,13 +2014,13 @@
         <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6054</v>
+        <v>0.7685</v>
       </c>
       <c r="T20" t="n">
         <v>0.0465</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5589</v>
+        <v>0.7221</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2178</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. HERMO ANTELO</t>
+          <t>S. MUJICA LANDAETA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4986</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0594</v>
+        <v>1.0006</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5580000000000001</v>
+        <v>-0.4013</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1364</v>
+        <v>0.2346</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-1.5645</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1364</v>
+        <v>1.799</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.4919</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.4781</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1364</v>
+        <v>-0.2573</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-1.0864</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1364</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1958</v>
+        <v>2.546</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1958</v>
+        <v>2.546</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1663</v>
+        <v>0.5273</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0594</v>
+        <v>0.5087</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2257</v>
+        <v>0.0185</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.7086</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. GARCÍA SINDIN</t>
+          <t>J. HERMO ANTELO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3051</v>
+        <v>0.3917</v>
       </c>
       <c r="E22" t="n">
-        <v>0.544</v>
+        <v>-0.0594</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2389</v>
+        <v>0.4511</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8091</v>
+        <v>0.1364</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9176</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2.7267</v>
+        <v>0.1364</v>
       </c>
       <c r="J22" t="n">
-        <v>2.2778</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1021</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2.1757</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4687</v>
+        <v>0.1364</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0197</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.551</v>
+        <v>0.1364</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4038</v>
+        <v>0.0594</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7546</v>
+        <v>-0.0594</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3508</v>
+        <v>0.1188</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5609</v>
+        <v>-0.549</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0969</v>
+        <v>-0.3015</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4641</v>
+        <v>-0.2474</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2935</v>
@@ -2248,13 +2248,13 @@
         <v>0.9792</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0301</v>
+        <v>-0.0181</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4029</v>
+        <v>0.1982</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4329</v>
+        <v>-0.2163</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2166</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1739</v>
+        <v>-0.7486</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3053</v>
+        <v>-0.1796</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8686</v>
+        <v>-0.569</v>
       </c>
       <c r="G24" t="n">
         <v>0.455</v>
@@ -2326,13 +2326,13 @@
         <v>3.1336</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1749</v>
+        <v>0.2504</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2716</v>
+        <v>-0.1459</v>
       </c>
       <c r="U24" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.3963</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4332</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>16.2894</v>
+        <v>17.6538</v>
       </c>
       <c r="E25" t="n">
-        <v>8.093700000000002</v>
+        <v>8.093799999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>8.195599999999999</v>
+        <v>9.560099999999998</v>
       </c>
       <c r="G25" t="n">
-        <v>9.728999999999999</v>
+        <v>9.729000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>1.0155</v>
@@ -2386,7 +2386,7 @@
         <v>5.1982</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8805999999999999</v>
+        <v>-0.8806</v>
       </c>
       <c r="N25" t="n">
         <v>-4.3956</v>
@@ -2404,16 +2404,16 @@
         <v>17.6261</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2231</v>
+        <v>3.5875</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9379999999999995</v>
+        <v>0.9381</v>
       </c>
       <c r="U25" t="n">
-        <v>1.2849</v>
+        <v>2.6496</v>
       </c>
       <c r="V25" t="n">
-        <v>-4.476</v>
+        <v>-4.475999999999999</v>
       </c>
       <c r="W25" t="n">
         <v>5.359599999999999</v>
